--- a/docs/data/raw/2026-07-12_ST.xlsx
+++ b/docs/data/raw/2026-07-12_ST.xlsx
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>3.1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>3.3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>7.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>5.5</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="21">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>6.9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>20</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="27">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>20</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>3.1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>3.3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>7.6</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="34">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>5.5</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="35">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
-        <v>6.9</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
-        <v>20</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="41">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>20</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>20</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="43">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
-        <v>3.1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>3.3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>7.6</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="48">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
-        <v>5.5</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="49">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
-        <v>6.9</v>
+        <v>41</v>
       </c>
     </row>
     <row r="51">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="52">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="53">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="n">
-        <v>20</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="55">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
-        <v>20</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="56">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="n">
-        <v>20</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="57">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>3.1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="59">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="n">
-        <v>3.3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="n">
-        <v>7.6</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="62">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="n">
-        <v>5.5</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="63">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="n">
-        <v>6.9</v>
+        <v>41</v>
       </c>
     </row>
     <row r="65">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="66">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="67">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="n">
-        <v>20</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="69">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="n">
-        <v>20</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="70">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="72">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="n">
-        <v>3.1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="73">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="n">
-        <v>3.3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="74">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="75">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="n">
-        <v>7.6</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="76">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="n">
-        <v>5.5</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="77">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="78">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="n">
-        <v>6.9</v>
+        <v>41</v>
       </c>
     </row>
     <row r="79">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="80">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="81">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="82">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="n">
-        <v>20</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="83">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="n">
-        <v>20</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="84">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="n">
-        <v>20</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="85">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="86">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="n">
-        <v>3.1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="87">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="n">
-        <v>3.2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="88">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="89">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="n">
-        <v>7.7</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="90">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="n">
-        <v>5.5</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="91">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="92">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="n">
-        <v>6.9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="93">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="94">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="95">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="96">
@@ -6027,7 +6027,7 @@
       </c>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="n">
-        <v>20</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="97">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="n">
-        <v>20</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="98">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="99">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="100">
@@ -6230,36 +6230,40 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>CAP FERRAT</t>
+          <t>CAP FERRAT(Scratched)</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>E Brown</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>K W Lui</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M100" t="n">
-        <v>112</v>
+        <v>50</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>6/9/2/7/-/8</t>
-        </is>
-      </c>
-      <c r="O100" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="P100" t="n">
-        <v>3.1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="101">
@@ -6292,7 +6296,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J101" t="n">
         <v>130</v>
@@ -6317,7 +6321,7 @@
       </c>
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="n">
-        <v>3.2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="102">
@@ -6350,7 +6354,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J102" t="n">
         <v>127</v>
@@ -6375,7 +6379,7 @@
       </c>
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="103">
@@ -6408,7 +6412,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J103" t="n">
         <v>125</v>
@@ -6433,7 +6437,7 @@
       </c>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="n">
-        <v>7.7</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="104">
@@ -6491,7 +6495,7 @@
       </c>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="n">
-        <v>5.5</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="105">
@@ -6524,7 +6528,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J105" t="n">
         <v>119</v>
@@ -6549,7 +6553,7 @@
       </c>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="106">
@@ -6582,7 +6586,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J106" t="n">
         <v>118</v>
@@ -6607,7 +6611,7 @@
       </c>
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="n">
-        <v>6.9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="107">
@@ -6640,7 +6644,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J107" t="n">
         <v>116</v>
@@ -6665,7 +6669,7 @@
       </c>
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="108">
@@ -6727,7 +6731,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="109">
@@ -6785,7 +6789,7 @@
       </c>
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="110">
@@ -6847,7 +6851,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>20</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="111">
@@ -6880,7 +6884,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J111" t="n">
         <v>115</v>
@@ -6905,7 +6909,7 @@
       </c>
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="n">
-        <v>20</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="112">
@@ -6938,7 +6942,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J112" t="n">
         <v>115</v>
@@ -6963,7 +6967,7 @@
       </c>
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="113">
@@ -7021,7 +7025,7 @@
       </c>
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="n">
-        <v>3.1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="114">
@@ -7079,7 +7083,7 @@
       </c>
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="n">
-        <v>3.2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="115">
@@ -7137,7 +7141,7 @@
       </c>
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="116">
@@ -7195,7 +7199,7 @@
       </c>
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="n">
-        <v>7.7</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="117">
@@ -7253,7 +7257,7 @@
       </c>
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="n">
-        <v>5.5</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="118">
@@ -7311,7 +7315,7 @@
       </c>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="119">
@@ -7369,7 +7373,7 @@
       </c>
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="n">
-        <v>6.9</v>
+        <v>41</v>
       </c>
     </row>
     <row r="120">
@@ -7427,7 +7431,7 @@
       </c>
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="121">
@@ -7485,7 +7489,7 @@
       </c>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="122">
@@ -7543,7 +7547,7 @@
       </c>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="123">
@@ -7601,7 +7605,7 @@
       </c>
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="n">
-        <v>20</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="124">
@@ -7663,7 +7667,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>20</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="125">
@@ -7721,7 +7725,7 @@
       </c>
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="n">
-        <v>20</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="126">
@@ -7779,7 +7783,7 @@
       </c>
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="127">
@@ -7837,7 +7841,7 @@
       </c>
       <c r="O127" t="inlineStr"/>
       <c r="P127" t="n">
-        <v>3.1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="128">
@@ -7895,7 +7899,7 @@
       </c>
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="n">
-        <v>3.2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="129">
@@ -7953,7 +7957,7 @@
       </c>
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="130">
@@ -8011,7 +8015,7 @@
       </c>
       <c r="O130" t="inlineStr"/>
       <c r="P130" t="n">
-        <v>7.7</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="131">
@@ -8069,7 +8073,7 @@
       </c>
       <c r="O131" t="inlineStr"/>
       <c r="P131" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="132">
@@ -8127,7 +8131,7 @@
       </c>
       <c r="O132" t="inlineStr"/>
       <c r="P132" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="133">
@@ -8185,7 +8189,7 @@
       </c>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="n">
-        <v>6.9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="134">
@@ -8243,7 +8247,7 @@
       </c>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="135">
@@ -8301,7 +8305,7 @@
       </c>
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="136">
@@ -8359,7 +8363,7 @@
       </c>
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="137">
@@ -8421,7 +8425,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>20</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="138">
@@ -8479,7 +8483,7 @@
       </c>
       <c r="O138" t="inlineStr"/>
       <c r="P138" t="n">
-        <v>20</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="139">
@@ -8537,7 +8541,7 @@
       </c>
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="140">
@@ -8595,7 +8599,7 @@
       </c>
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="141">
@@ -8653,7 +8657,7 @@
       </c>
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="n">
-        <v>3.1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="142">
@@ -8711,7 +8715,7 @@
       </c>
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="n">
-        <v>3.2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="143">
@@ -8769,7 +8773,7 @@
       </c>
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="144">
@@ -8827,7 +8831,7 @@
       </c>
       <c r="O144" t="inlineStr"/>
       <c r="P144" t="n">
-        <v>7.7</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="145">
@@ -8885,7 +8889,7 @@
       </c>
       <c r="O145" t="inlineStr"/>
       <c r="P145" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="146">
@@ -8943,7 +8947,7 @@
       </c>
       <c r="O146" t="inlineStr"/>
       <c r="P146" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="147">
@@ -9001,7 +9005,7 @@
       </c>
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="n">
-        <v>6.9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="148">
@@ -9059,7 +9063,7 @@
       </c>
       <c r="O148" t="inlineStr"/>
       <c r="P148" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="149">
@@ -9117,7 +9121,7 @@
       </c>
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="150">
@@ -9175,7 +9179,7 @@
       </c>
       <c r="O150" t="inlineStr"/>
       <c r="P150" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="151">
@@ -9233,7 +9237,7 @@
       </c>
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="n">
-        <v>20</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="152">
@@ -9291,7 +9295,7 @@
       </c>
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="n">
-        <v>20</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="153">
@@ -9349,7 +9353,7 @@
       </c>
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="154">
@@ -9407,7 +9411,7 @@
       </c>
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -9538,10 +9542,10 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>3.1</v>
+        <v>17</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="M2" t="n">
         <v>14</v>
@@ -9592,10 +9596,10 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>15</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="M3" t="n">
         <v>14</v>
@@ -9646,10 +9650,10 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="L4" t="n">
-        <v>3.8</v>
+        <v>10</v>
       </c>
       <c r="M4" t="n">
         <v>14</v>
@@ -9700,10 +9704,10 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>7.7</v>
+        <v>3.9</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="M5" t="n">
         <v>14</v>
@@ -9754,10 +9758,10 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>5.5</v>
+        <v>8.9</v>
       </c>
       <c r="L6" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="M6" t="n">
         <v>14</v>
@@ -9808,10 +9812,10 @@
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="M7" t="n">
         <v>14</v>
@@ -9862,10 +9866,10 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>6.9</v>
+        <v>41</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8</v>
+        <v>11</v>
       </c>
       <c r="M8" t="n">
         <v>14</v>
@@ -9916,9 +9920,11 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>20</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.1</v>
+      </c>
       <c r="M9" t="n">
         <v>14</v>
       </c>
@@ -9968,9 +9974,11 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>20</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6.4</v>
+      </c>
       <c r="M10" t="n">
         <v>14</v>
       </c>
@@ -10020,9 +10028,11 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>20</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3.2</v>
+      </c>
       <c r="M11" t="n">
         <v>14</v>
       </c>
@@ -10072,9 +10082,11 @@
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
+        <v>6.3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.3</v>
+      </c>
       <c r="M12" t="n">
         <v>14</v>
       </c>
@@ -10128,9 +10140,11 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>20</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.7</v>
+      </c>
       <c r="M13" t="n">
         <v>14</v>
       </c>
@@ -10180,9 +10194,11 @@
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>20</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
+        <v>9.1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.9</v>
+      </c>
       <c r="M14" t="n">
         <v>14</v>
       </c>
@@ -10232,9 +10248,11 @@
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>20</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5.3</v>
+      </c>
       <c r="M15" t="n">
         <v>14</v>
       </c>
@@ -10370,10 +10388,10 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>3.1</v>
+        <v>17</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="M2" t="n">
         <v>14</v>
@@ -10424,10 +10442,10 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>15</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="M3" t="n">
         <v>14</v>
@@ -10478,10 +10496,10 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="L4" t="n">
-        <v>3.8</v>
+        <v>10</v>
       </c>
       <c r="M4" t="n">
         <v>14</v>
@@ -10532,10 +10550,10 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>7.7</v>
+        <v>3.9</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="M5" t="n">
         <v>14</v>
@@ -10586,10 +10604,10 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="L6" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="M6" t="n">
         <v>14</v>
@@ -10640,10 +10658,10 @@
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="M7" t="n">
         <v>14</v>
@@ -10694,10 +10712,10 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>6.9</v>
+        <v>42</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8</v>
+        <v>11</v>
       </c>
       <c r="M8" t="n">
         <v>14</v>
@@ -10748,9 +10766,11 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>20</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.1</v>
+      </c>
       <c r="M9" t="n">
         <v>14</v>
       </c>
@@ -10800,9 +10820,11 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>20</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6.4</v>
+      </c>
       <c r="M10" t="n">
         <v>14</v>
       </c>
@@ -10852,9 +10874,11 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>20</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3.2</v>
+      </c>
       <c r="M11" t="n">
         <v>14</v>
       </c>
@@ -10908,9 +10932,11 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
+        <v>6.4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.3</v>
+      </c>
       <c r="M12" t="n">
         <v>14</v>
       </c>
@@ -10960,9 +10986,11 @@
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>20</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
+        <v>8.1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.7</v>
+      </c>
       <c r="M13" t="n">
         <v>14</v>
       </c>
@@ -11012,9 +11040,11 @@
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>20</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.9</v>
+      </c>
       <c r="M14" t="n">
         <v>14</v>
       </c>
@@ -11064,9 +11094,11 @@
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>20</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5.3</v>
+      </c>
       <c r="M15" t="n">
         <v>14</v>
       </c>
@@ -11202,10 +11234,10 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>3.1</v>
+        <v>17</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="M2" t="n">
         <v>14</v>
@@ -11256,10 +11288,10 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>15</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="M3" t="n">
         <v>14</v>
@@ -11310,10 +11342,10 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="L4" t="n">
-        <v>3.8</v>
+        <v>10</v>
       </c>
       <c r="M4" t="n">
         <v>14</v>
@@ -11364,10 +11396,10 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>7.7</v>
+        <v>3.9</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="M5" t="n">
         <v>14</v>
@@ -11418,10 +11450,10 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="L6" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="M6" t="n">
         <v>14</v>
@@ -11472,10 +11504,10 @@
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="M7" t="n">
         <v>14</v>
@@ -11526,10 +11558,10 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>6.9</v>
+        <v>42</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8</v>
+        <v>11</v>
       </c>
       <c r="M8" t="n">
         <v>14</v>
@@ -11580,9 +11612,11 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>20</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.1</v>
+      </c>
       <c r="M9" t="n">
         <v>14</v>
       </c>
@@ -11632,9 +11666,11 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>20</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6.4</v>
+      </c>
       <c r="M10" t="n">
         <v>14</v>
       </c>
@@ -11684,9 +11720,11 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>20</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3.2</v>
+      </c>
       <c r="M11" t="n">
         <v>14</v>
       </c>
@@ -11736,9 +11774,11 @@
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
+        <v>6.4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.3</v>
+      </c>
       <c r="M12" t="n">
         <v>14</v>
       </c>
@@ -11788,9 +11828,11 @@
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>20</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
+        <v>8.1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.7</v>
+      </c>
       <c r="M13" t="n">
         <v>14</v>
       </c>
@@ -11840,9 +11882,11 @@
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>20</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.9</v>
+      </c>
       <c r="M14" t="n">
         <v>14</v>
       </c>
@@ -11892,9 +11936,11 @@
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>20</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5.3</v>
+      </c>
       <c r="M15" t="n">
         <v>14</v>
       </c>
@@ -19992,7 +20038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E78"/>
+  <dimension ref="A1:E155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20032,14 +20078,14 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3.1</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
@@ -20053,14 +20099,14 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3.3</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
@@ -20074,14 +20120,14 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
@@ -20095,14 +20141,14 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7.6</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
@@ -20116,14 +20162,14 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5.5</v>
+        <v>8.9</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
@@ -20137,14 +20183,14 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
@@ -20158,167 +20204,167 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6.9</v>
+        <v>42</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8</v>
+        <v>12</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.1</v>
+        <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3.3</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2</v>
+        <v>6.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7.6</v>
+        <v>6.3</v>
       </c>
       <c r="D12" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
         <v>2.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6.9</v>
+        <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8</v>
+        <v>5.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -20326,20 +20372,20 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3.1</v>
+        <v>17</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -20347,20 +20393,20 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3.3</v>
+        <v>15</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -20368,20 +20414,20 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>3.7</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -20389,20 +20435,20 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7.6</v>
+        <v>3.9</v>
       </c>
       <c r="D19" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -20410,20 +20456,20 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5.5</v>
+        <v>8.9</v>
       </c>
       <c r="D20" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -20431,20 +20477,20 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -20452,167 +20498,167 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6.9</v>
+        <v>41</v>
       </c>
       <c r="D22" t="n">
-        <v>1.8</v>
+        <v>12</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3.1</v>
+        <v>17</v>
       </c>
       <c r="D23" t="n">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3.3</v>
+        <v>26</v>
       </c>
       <c r="D24" t="n">
-        <v>1.2</v>
+        <v>6.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D25" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>7.6</v>
+        <v>6.3</v>
       </c>
       <c r="D26" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>13</v>
+        <v>9.1</v>
       </c>
       <c r="D28" t="n">
         <v>2.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6.9</v>
+        <v>21</v>
       </c>
       <c r="D29" t="n">
-        <v>1.8</v>
+        <v>5.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -20620,20 +20666,20 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3.1</v>
+        <v>17</v>
       </c>
       <c r="D30" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -20641,20 +20687,20 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3.3</v>
+        <v>15</v>
       </c>
       <c r="D31" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -20662,20 +20708,20 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="D32" t="n">
-        <v>3.8</v>
+        <v>10</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -20683,20 +20729,20 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7.6</v>
+        <v>3.9</v>
       </c>
       <c r="D33" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -20704,20 +20750,20 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5.5</v>
+        <v>8.9</v>
       </c>
       <c r="D34" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -20725,20 +20771,20 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D35" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -20746,167 +20792,167 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>6.9</v>
+        <v>41</v>
       </c>
       <c r="D36" t="n">
-        <v>1.8</v>
+        <v>12</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3.1</v>
+        <v>17</v>
       </c>
       <c r="D37" t="n">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3.2</v>
+        <v>26</v>
       </c>
       <c r="D38" t="n">
-        <v>1.2</v>
+        <v>6.3</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D39" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>7.7</v>
+        <v>6.3</v>
       </c>
       <c r="D40" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>13</v>
+        <v>9.1</v>
       </c>
       <c r="D42" t="n">
         <v>2.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6.9</v>
+        <v>21</v>
       </c>
       <c r="D43" t="n">
-        <v>1.8</v>
+        <v>5.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -20914,20 +20960,20 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3.1</v>
+        <v>17</v>
       </c>
       <c r="D44" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -20935,20 +20981,20 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3.2</v>
+        <v>15</v>
       </c>
       <c r="D45" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -20956,20 +21002,20 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="D46" t="n">
-        <v>3.8</v>
+        <v>10</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -20977,20 +21023,20 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>7.7</v>
+        <v>3.9</v>
       </c>
       <c r="D47" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -20998,20 +21044,20 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5.5</v>
+        <v>8.9</v>
       </c>
       <c r="D48" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -21019,20 +21065,20 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D49" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -21040,167 +21086,167 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6.9</v>
+        <v>41</v>
       </c>
       <c r="D50" t="n">
-        <v>1.8</v>
+        <v>11</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3.1</v>
+        <v>17</v>
       </c>
       <c r="D51" t="n">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3.2</v>
+        <v>26</v>
       </c>
       <c r="D52" t="n">
-        <v>1.2</v>
+        <v>6.3</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D53" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>7.7</v>
+        <v>6.3</v>
       </c>
       <c r="D54" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>5.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D55" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
+        <v>5</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
         <v>9</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>13</v>
       </c>
       <c r="D56" t="n">
         <v>2.9</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>6.9</v>
+        <v>21</v>
       </c>
       <c r="D57" t="n">
-        <v>1.8</v>
+        <v>5.3</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -21208,20 +21254,20 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3.1</v>
+        <v>17</v>
       </c>
       <c r="D58" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -21229,41 +21275,41 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3.2</v>
+        <v>15</v>
       </c>
       <c r="D59" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
+        <v>6</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>35</v>
+      </c>
+      <c r="D60" t="n">
         <v>10</v>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>17</v>
-      </c>
-      <c r="D60" t="n">
-        <v>3.8</v>
-      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -21271,20 +21317,20 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>7.7</v>
+        <v>3.9</v>
       </c>
       <c r="D61" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -21292,20 +21338,20 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>5.5</v>
+        <v>8.9</v>
       </c>
       <c r="D62" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -21313,20 +21359,20 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D63" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -21334,167 +21380,167 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6.9</v>
+        <v>41</v>
       </c>
       <c r="D64" t="n">
-        <v>1.8</v>
+        <v>12</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3.1</v>
+        <v>17</v>
       </c>
       <c r="D65" t="n">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3.2</v>
+        <v>26</v>
       </c>
       <c r="D66" t="n">
-        <v>1.2</v>
+        <v>6.3</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
+        <v>6</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
         <v>11</v>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>17</v>
-      </c>
       <c r="D67" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>7.7</v>
+        <v>6.3</v>
       </c>
       <c r="D68" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>5.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D69" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>13</v>
+        <v>9.1</v>
       </c>
       <c r="D70" t="n">
         <v>2.9</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>6.9</v>
+        <v>21</v>
       </c>
       <c r="D71" t="n">
-        <v>1.8</v>
+        <v>5.3</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -21502,20 +21548,20 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3.1</v>
+        <v>17</v>
       </c>
       <c r="D72" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -21523,20 +21569,20 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3.2</v>
+        <v>15</v>
       </c>
       <c r="D73" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -21544,20 +21590,20 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="D74" t="n">
-        <v>3.8</v>
+        <v>10</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -21565,20 +21611,20 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>7.7</v>
+        <v>3.9</v>
       </c>
       <c r="D75" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -21586,20 +21632,20 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>5.5</v>
+        <v>8.9</v>
       </c>
       <c r="D76" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -21607,35 +21653,1652 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D77" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>12:13:09</t>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
+        <v>7</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>42</v>
+      </c>
+      <c r="D78" t="n">
+        <v>11</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>7</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>17</v>
+      </c>
+      <c r="D79" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>7</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>26</v>
+      </c>
+      <c r="D80" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>7</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>11</v>
+      </c>
+      <c r="D81" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>7</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="D82" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>7</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="D83" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>7</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>9</v>
+      </c>
+      <c r="D84" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>7</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>21</v>
+      </c>
+      <c r="D85" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>8</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>17</v>
+      </c>
+      <c r="D86" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>8</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>15</v>
+      </c>
+      <c r="D87" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>8</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>35</v>
+      </c>
+      <c r="D88" t="n">
+        <v>10</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>8</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D89" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>8</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="D90" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>8</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>16</v>
+      </c>
+      <c r="D91" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>8</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>42</v>
+      </c>
+      <c r="D92" t="n">
+        <v>11</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>8</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>17</v>
+      </c>
+      <c r="D93" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>8</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>26</v>
+      </c>
+      <c r="D94" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>8</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>11</v>
+      </c>
+      <c r="D95" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>8</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="D96" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>8</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="D97" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>8</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>9</v>
+      </c>
+      <c r="D98" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>8</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>21</v>
+      </c>
+      <c r="D99" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>9</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>17</v>
+      </c>
+      <c r="D100" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>9</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>15</v>
+      </c>
+      <c r="D101" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>9</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>35</v>
+      </c>
+      <c r="D102" t="n">
+        <v>10</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>9</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D103" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>9</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="D104" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>9</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>16</v>
+      </c>
+      <c r="D105" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>9</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>41</v>
+      </c>
+      <c r="D106" t="n">
+        <v>11</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>9</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>17</v>
+      </c>
+      <c r="D107" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>9</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>26</v>
+      </c>
+      <c r="D108" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>9</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>11</v>
+      </c>
+      <c r="D109" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>9</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="D110" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>9</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="D111" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>9</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="D112" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>9</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>21</v>
+      </c>
+      <c r="D113" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>10</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>17</v>
+      </c>
+      <c r="D114" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>10</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>15</v>
+      </c>
+      <c r="D115" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>10</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>35</v>
+      </c>
+      <c r="D116" t="n">
+        <v>10</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>10</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>10</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>9</v>
+      </c>
+      <c r="D118" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>10</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>16</v>
+      </c>
+      <c r="D119" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>10</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>42</v>
+      </c>
+      <c r="D120" t="n">
+        <v>11</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>10</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>17</v>
+      </c>
+      <c r="D121" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>10</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>26</v>
+      </c>
+      <c r="D122" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>10</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>11</v>
+      </c>
+      <c r="D123" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>10</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="D124" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>10</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="D125" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>10</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>9</v>
+      </c>
+      <c r="D126" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>10</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>21</v>
+      </c>
+      <c r="D127" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>11</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>17</v>
+      </c>
+      <c r="D128" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>11</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>15</v>
+      </c>
+      <c r="D129" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>11</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>35</v>
+      </c>
+      <c r="D130" t="n">
+        <v>10</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>11</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D131" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>11</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>9</v>
+      </c>
+      <c r="D132" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>11</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>16</v>
+      </c>
+      <c r="D133" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>11</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>42</v>
+      </c>
+      <c r="D134" t="n">
+        <v>11</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>11</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>17</v>
+      </c>
+      <c r="D135" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>11</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>26</v>
+      </c>
+      <c r="D136" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>11</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>11</v>
+      </c>
+      <c r="D137" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>11</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="D138" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>11</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="D139" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>11</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>9</v>
+      </c>
+      <c r="D140" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>11</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>21</v>
+      </c>
+      <c r="D141" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
         <v>12</v>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>17</v>
+      </c>
+      <c r="D142" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>12</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>15</v>
+      </c>
+      <c r="D143" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>12</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>35</v>
+      </c>
+      <c r="D144" t="n">
+        <v>10</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>12</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>12</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>9</v>
+      </c>
+      <c r="D146" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>12</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>16</v>
+      </c>
+      <c r="D147" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>12</v>
+      </c>
+      <c r="B148" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C78" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="D78" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>12:13:09</t>
+      <c r="C148" t="n">
+        <v>42</v>
+      </c>
+      <c r="D148" t="n">
+        <v>11</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>12</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>17</v>
+      </c>
+      <c r="D149" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>12</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>26</v>
+      </c>
+      <c r="D150" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>12</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>11</v>
+      </c>
+      <c r="D151" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>12</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="D152" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>12</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="D153" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>12</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>9</v>
+      </c>
+      <c r="D154" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>12</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>21</v>
+      </c>
+      <c r="D155" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>12:33:39</t>
         </is>
       </c>
     </row>
@@ -22566,10 +24229,10 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>3.1</v>
+        <v>17</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="M2" t="n">
         <v>14</v>
@@ -22620,10 +24283,10 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>15</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="M3" t="n">
         <v>14</v>
@@ -22674,10 +24337,10 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="L4" t="n">
-        <v>3.7</v>
+        <v>10</v>
       </c>
       <c r="M4" t="n">
         <v>14</v>
@@ -22728,10 +24391,10 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>7.6</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="M5" t="n">
         <v>14</v>
@@ -22782,10 +24445,10 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>5.5</v>
+        <v>8.9</v>
       </c>
       <c r="L6" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="M6" t="n">
         <v>14</v>
@@ -22836,10 +24499,10 @@
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="M7" t="n">
         <v>14</v>
@@ -22890,10 +24553,10 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>6.9</v>
+        <v>42</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8</v>
+        <v>12</v>
       </c>
       <c r="M8" t="n">
         <v>14</v>
@@ -22944,9 +24607,11 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>20</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.1</v>
+      </c>
       <c r="M9" t="n">
         <v>14</v>
       </c>
@@ -22996,9 +24661,11 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>20</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6.3</v>
+      </c>
       <c r="M10" t="n">
         <v>14</v>
       </c>
@@ -23048,9 +24715,11 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>20</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3.2</v>
+      </c>
       <c r="M11" t="n">
         <v>14</v>
       </c>
@@ -23100,9 +24769,11 @@
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
+        <v>6.3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.3</v>
+      </c>
       <c r="M12" t="n">
         <v>14</v>
       </c>
@@ -23152,9 +24823,11 @@
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>20</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.6</v>
+      </c>
       <c r="M13" t="n">
         <v>14</v>
       </c>
@@ -23204,9 +24877,11 @@
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>20</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.9</v>
+      </c>
       <c r="M14" t="n">
         <v>14</v>
       </c>
@@ -23256,9 +24931,11 @@
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>20</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5.4</v>
+      </c>
       <c r="M15" t="n">
         <v>14</v>
       </c>
@@ -23394,10 +25071,10 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>3.1</v>
+        <v>17</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="M2" t="n">
         <v>14</v>
@@ -23448,10 +25125,10 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>15</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="M3" t="n">
         <v>14</v>
@@ -23502,10 +25179,10 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="L4" t="n">
-        <v>3.8</v>
+        <v>10</v>
       </c>
       <c r="M4" t="n">
         <v>14</v>
@@ -23556,10 +25233,10 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>7.6</v>
+        <v>3.9</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="M5" t="n">
         <v>14</v>
@@ -23610,10 +25287,10 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>5.5</v>
+        <v>8.9</v>
       </c>
       <c r="L6" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="M6" t="n">
         <v>14</v>
@@ -23664,10 +25341,10 @@
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="M7" t="n">
         <v>14</v>
@@ -23718,10 +25395,10 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>6.9</v>
+        <v>41</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8</v>
+        <v>12</v>
       </c>
       <c r="M8" t="n">
         <v>14</v>
@@ -23772,9 +25449,11 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>20</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.1</v>
+      </c>
       <c r="M9" t="n">
         <v>14</v>
       </c>
@@ -23824,9 +25503,11 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>20</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6.3</v>
+      </c>
       <c r="M10" t="n">
         <v>14</v>
       </c>
@@ -23876,9 +25557,11 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>20</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3.2</v>
+      </c>
       <c r="M11" t="n">
         <v>14</v>
       </c>
@@ -23928,9 +25611,11 @@
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
+        <v>6.3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.3</v>
+      </c>
       <c r="M12" t="n">
         <v>14</v>
       </c>
@@ -23980,9 +25665,11 @@
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>20</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.6</v>
+      </c>
       <c r="M13" t="n">
         <v>14</v>
       </c>
@@ -24032,9 +25719,11 @@
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>20</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
+        <v>9.1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.9</v>
+      </c>
       <c r="M14" t="n">
         <v>14</v>
       </c>
@@ -24084,9 +25773,11 @@
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>20</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5.3</v>
+      </c>
       <c r="M15" t="n">
         <v>14</v>
       </c>
@@ -24222,10 +25913,10 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>3.1</v>
+        <v>17</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="M2" t="n">
         <v>14</v>
@@ -24276,10 +25967,10 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>15</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="M3" t="n">
         <v>14</v>
@@ -24330,10 +26021,10 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="L4" t="n">
-        <v>3.7</v>
+        <v>10</v>
       </c>
       <c r="M4" t="n">
         <v>14</v>
@@ -24384,10 +26075,10 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>7.6</v>
+        <v>3.9</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="M5" t="n">
         <v>14</v>
@@ -24438,10 +26129,10 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>5.5</v>
+        <v>8.9</v>
       </c>
       <c r="L6" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="M6" t="n">
         <v>14</v>
@@ -24492,10 +26183,10 @@
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="M7" t="n">
         <v>14</v>
@@ -24546,10 +26237,10 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>6.9</v>
+        <v>41</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8</v>
+        <v>12</v>
       </c>
       <c r="M8" t="n">
         <v>14</v>
@@ -24600,9 +26291,11 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>20</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.1</v>
+      </c>
       <c r="M9" t="n">
         <v>14</v>
       </c>
@@ -24652,9 +26345,11 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>20</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6.3</v>
+      </c>
       <c r="M10" t="n">
         <v>14</v>
       </c>
@@ -24704,9 +26399,11 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>20</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3.2</v>
+      </c>
       <c r="M11" t="n">
         <v>14</v>
       </c>
@@ -24756,9 +26453,11 @@
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
+        <v>6.3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.3</v>
+      </c>
       <c r="M12" t="n">
         <v>14</v>
       </c>
@@ -24808,9 +26507,11 @@
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>20</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.6</v>
+      </c>
       <c r="M13" t="n">
         <v>14</v>
       </c>
@@ -24860,9 +26561,11 @@
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>20</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
+        <v>9.1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.9</v>
+      </c>
       <c r="M14" t="n">
         <v>14</v>
       </c>
@@ -24912,9 +26615,11 @@
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>20</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5.4</v>
+      </c>
       <c r="M15" t="n">
         <v>14</v>
       </c>
@@ -25050,10 +26755,10 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>3.1</v>
+        <v>17</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="M2" t="n">
         <v>14</v>
@@ -25104,10 +26809,10 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>15</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="M3" t="n">
         <v>14</v>
@@ -25158,10 +26863,10 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="L4" t="n">
-        <v>3.8</v>
+        <v>10</v>
       </c>
       <c r="M4" t="n">
         <v>14</v>
@@ -25212,10 +26917,10 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>7.6</v>
+        <v>3.9</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="M5" t="n">
         <v>14</v>
@@ -25266,10 +26971,10 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>5.5</v>
+        <v>8.9</v>
       </c>
       <c r="L6" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="M6" t="n">
         <v>14</v>
@@ -25320,10 +27025,10 @@
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="M7" t="n">
         <v>14</v>
@@ -25374,10 +27079,10 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>6.9</v>
+        <v>41</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8</v>
+        <v>11</v>
       </c>
       <c r="M8" t="n">
         <v>14</v>
@@ -25428,9 +27133,11 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>20</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.1</v>
+      </c>
       <c r="M9" t="n">
         <v>14</v>
       </c>
@@ -25480,9 +27187,11 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>20</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6.3</v>
+      </c>
       <c r="M10" t="n">
         <v>14</v>
       </c>
@@ -25532,9 +27241,11 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>20</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3.2</v>
+      </c>
       <c r="M11" t="n">
         <v>14</v>
       </c>
@@ -25584,9 +27295,11 @@
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
+        <v>6.3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.3</v>
+      </c>
       <c r="M12" t="n">
         <v>14</v>
       </c>
@@ -25636,9 +27349,11 @@
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>20</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.6</v>
+      </c>
       <c r="M13" t="n">
         <v>14</v>
       </c>
@@ -25688,9 +27403,11 @@
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>20</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.9</v>
+      </c>
       <c r="M14" t="n">
         <v>14</v>
       </c>
@@ -25740,9 +27457,11 @@
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>20</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5.3</v>
+      </c>
       <c r="M15" t="n">
         <v>14</v>
       </c>
@@ -25878,10 +27597,10 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>3.1</v>
+        <v>17</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="M2" t="n">
         <v>14</v>
@@ -25932,10 +27651,10 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>15</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="M3" t="n">
         <v>14</v>
@@ -25986,10 +27705,10 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="L4" t="n">
-        <v>3.8</v>
+        <v>10</v>
       </c>
       <c r="M4" t="n">
         <v>14</v>
@@ -26040,10 +27759,10 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>7.6</v>
+        <v>3.9</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="M5" t="n">
         <v>14</v>
@@ -26094,10 +27813,10 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>5.5</v>
+        <v>8.9</v>
       </c>
       <c r="L6" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="M6" t="n">
         <v>14</v>
@@ -26148,10 +27867,10 @@
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="M7" t="n">
         <v>14</v>
@@ -26202,10 +27921,10 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>6.9</v>
+        <v>41</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8</v>
+        <v>12</v>
       </c>
       <c r="M8" t="n">
         <v>14</v>
@@ -26256,9 +27975,11 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>20</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.1</v>
+      </c>
       <c r="M9" t="n">
         <v>14</v>
       </c>
@@ -26308,9 +28029,11 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>20</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6.3</v>
+      </c>
       <c r="M10" t="n">
         <v>14</v>
       </c>
@@ -26360,9 +28083,11 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>20</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3.2</v>
+      </c>
       <c r="M11" t="n">
         <v>14</v>
       </c>
@@ -26412,9 +28137,11 @@
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
+        <v>6.3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.3</v>
+      </c>
       <c r="M12" t="n">
         <v>14</v>
       </c>
@@ -26464,9 +28191,11 @@
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>20</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.6</v>
+      </c>
       <c r="M13" t="n">
         <v>14</v>
       </c>
@@ -26516,9 +28245,11 @@
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>20</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
+        <v>9.1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.9</v>
+      </c>
       <c r="M14" t="n">
         <v>14</v>
       </c>
@@ -26568,9 +28299,11 @@
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>20</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5.3</v>
+      </c>
       <c r="M15" t="n">
         <v>14</v>
       </c>
@@ -26706,10 +28439,10 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>3.1</v>
+        <v>17</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="M2" t="n">
         <v>14</v>
@@ -26760,10 +28493,10 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>15</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="M3" t="n">
         <v>14</v>
@@ -26814,10 +28547,10 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="L4" t="n">
-        <v>3.8</v>
+        <v>10</v>
       </c>
       <c r="M4" t="n">
         <v>14</v>
@@ -26868,10 +28601,10 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>7.7</v>
+        <v>3.9</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="M5" t="n">
         <v>14</v>
@@ -26922,10 +28655,10 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>5.5</v>
+        <v>8.9</v>
       </c>
       <c r="L6" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="M6" t="n">
         <v>14</v>
@@ -26976,10 +28709,10 @@
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="M7" t="n">
         <v>14</v>
@@ -27030,10 +28763,10 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>6.9</v>
+        <v>42</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8</v>
+        <v>11</v>
       </c>
       <c r="M8" t="n">
         <v>14</v>
@@ -27084,9 +28817,11 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>20</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.1</v>
+      </c>
       <c r="M9" t="n">
         <v>14</v>
       </c>
@@ -27136,9 +28871,11 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>20</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6.3</v>
+      </c>
       <c r="M10" t="n">
         <v>14</v>
       </c>
@@ -27188,9 +28925,11 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>20</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3.2</v>
+      </c>
       <c r="M11" t="n">
         <v>14</v>
       </c>
@@ -27240,9 +28979,11 @@
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
+        <v>6.3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.3</v>
+      </c>
       <c r="M12" t="n">
         <v>14</v>
       </c>
@@ -27292,9 +29033,11 @@
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>20</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.6</v>
+      </c>
       <c r="M13" t="n">
         <v>14</v>
       </c>
@@ -27344,9 +29087,11 @@
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>20</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.9</v>
+      </c>
       <c r="M14" t="n">
         <v>14</v>
       </c>
@@ -27396,9 +29141,11 @@
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>20</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5.3</v>
+      </c>
       <c r="M15" t="n">
         <v>14</v>
       </c>
@@ -27505,45 +29252,49 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CAP FERRAT</t>
+          <t>CAP FERRAT(Scratched)</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>E Brown</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>K W Lui</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>112</v>
+        <v>50</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6/9/2/7/-/8</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K2" t="n">
-        <v>3.1</v>
+        <v>17</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="M2" t="n">
         <v>13</v>
       </c>
       <c r="N2" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="3">
@@ -27563,7 +29314,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
         <v>130</v>
@@ -27588,16 +29339,16 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>15</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="M3" t="n">
         <v>13</v>
       </c>
       <c r="N3" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="4">
@@ -27617,7 +29368,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
         <v>127</v>
@@ -27642,16 +29393,16 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="L4" t="n">
-        <v>3.8</v>
+        <v>10</v>
       </c>
       <c r="M4" t="n">
         <v>13</v>
       </c>
       <c r="N4" t="n">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="5">
@@ -27671,7 +29422,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
         <v>125</v>
@@ -27696,16 +29447,16 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>7.7</v>
+        <v>3.9</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="M5" t="n">
         <v>13</v>
       </c>
       <c r="N5" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -27750,10 +29501,10 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>5.5</v>
+        <v>8.9</v>
       </c>
       <c r="L6" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="M6" t="n">
         <v>13</v>
@@ -27779,7 +29530,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
         <v>119</v>
@@ -27804,16 +29555,16 @@
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="M7" t="n">
         <v>13</v>
       </c>
       <c r="N7" t="n">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="8">
@@ -27833,7 +29584,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
         <v>118</v>
@@ -27858,16 +29609,16 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>6.9</v>
+        <v>42</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8</v>
+        <v>11</v>
       </c>
       <c r="M8" t="n">
         <v>13</v>
       </c>
       <c r="N8" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="9">
@@ -27887,7 +29638,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
         <v>116</v>
@@ -27912,14 +29663,16 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>20</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.1</v>
+      </c>
       <c r="M9" t="n">
         <v>13</v>
       </c>
       <c r="N9" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="10">
@@ -27968,9 +29721,11 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>20</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6.4</v>
+      </c>
       <c r="M10" t="n">
         <v>13</v>
       </c>
@@ -28020,9 +29775,11 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>20</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3.2</v>
+      </c>
       <c r="M11" t="n">
         <v>13</v>
       </c>
@@ -28076,9 +29833,11 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
+        <v>6.3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.3</v>
+      </c>
       <c r="M12" t="n">
         <v>13</v>
       </c>
@@ -28103,7 +29862,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
         <v>115</v>
@@ -28128,14 +29887,16 @@
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>20</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.7</v>
+      </c>
       <c r="M13" t="n">
         <v>13</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="14">
@@ -28155,7 +29916,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
         <v>115</v>
@@ -28180,14 +29941,16 @@
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>20</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.9</v>
+      </c>
       <c r="M14" t="n">
         <v>13</v>
       </c>
       <c r="N14" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
     </row>
   </sheetData>
